--- a/data/dividends_info_20260706.xlsx
+++ b/data/dividends_info_20260706.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>61.88000106811523</v>
+        <v>63.36000061035156</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1454427899911173</v>
+        <v>0.1420454531771202</v>
       </c>
       <c r="J2" t="n">
         <v>252</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66.55000305175781</v>
+        <v>66.65000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.051840673028355</v>
+        <v>1.050262541596797</v>
       </c>
       <c r="J3" t="n">
         <v>231</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.800000190734863</v>
+        <v>9.920000076293945</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6122448860432199</v>
+        <v>0.6048387050256521</v>
       </c>
       <c r="J4" t="n">
         <v>161</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>61.88000106811523</v>
+        <v>63.36000061035156</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1454427899911173</v>
+        <v>0.1420454531771202</v>
       </c>
       <c r="J6" t="n">
         <v>161</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.134999990463257</v>
+        <v>2.105000019073486</v>
       </c>
       <c r="I7" t="n">
-        <v>3.606557393159162</v>
+        <v>3.65795721151069</v>
       </c>
       <c r="J7" t="n">
         <v>140</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20.36499977111816</v>
+        <v>20.38999938964844</v>
       </c>
       <c r="I8" t="n">
-        <v>1.325804090520623</v>
+        <v>1.324178558519591</v>
       </c>
       <c r="J8" t="n">
         <v>140</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.019999980926514</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="I9" t="n">
-        <v>3.322259146738715</v>
+        <v>3.300330064166073</v>
       </c>
       <c r="J9" t="n">
         <v>133</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.949999809265137</v>
+        <v>4.929999828338623</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7676767972571169</v>
+        <v>0.7707911018894649</v>
       </c>
       <c r="J13" t="n">
         <v>84</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20.36499977111816</v>
+        <v>20.38999938964844</v>
       </c>
       <c r="I14" t="n">
-        <v>1.325804090520623</v>
+        <v>1.324178558519591</v>
       </c>
       <c r="J14" t="n">
         <v>77</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>61.88000106811523</v>
+        <v>63.36000061035156</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1454427899911173</v>
+        <v>0.1420454531771202</v>
       </c>
       <c r="J15" t="n">
         <v>77</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.940000057220459</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="I16" t="n">
-        <v>5.050505001853162</v>
+        <v>5.016722392025687</v>
       </c>
       <c r="J16" t="n">
         <v>70</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.949999809265137</v>
+        <v>4.929999828338623</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7676767972571169</v>
+        <v>0.7707911018894649</v>
       </c>
       <c r="J18" t="n">
         <v>28</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.800000190734863</v>
+        <v>5.789999961853027</v>
       </c>
       <c r="I19" t="n">
-        <v>4.310344685839137</v>
+        <v>4.317789320329981</v>
       </c>
       <c r="J19" t="n">
         <v>21</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.170000076293945</v>
+        <v>4.110000133514404</v>
       </c>
       <c r="I20" t="n">
-        <v>3.357314087255939</v>
+        <v>3.40632592340789</v>
       </c>
       <c r="J20" t="n">
         <v>14</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.19999980926514</v>
+        <v>10.14599990844727</v>
       </c>
       <c r="I21" t="n">
-        <v>2.549019655508521</v>
+        <v>2.562586264006681</v>
       </c>
       <c r="J21" t="n">
         <v>14</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.69999980926514</v>
+        <v>14.68000030517578</v>
       </c>
       <c r="I22" t="n">
-        <v>4.081632706021065</v>
+        <v>4.087193375523676</v>
       </c>
       <c r="J22" t="n">
         <v>14</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.924999952316284</v>
+        <v>2.911999940872192</v>
       </c>
       <c r="I23" t="n">
-        <v>7.521367643981798</v>
+        <v>7.554945208347304</v>
       </c>
       <c r="J23" t="n">
         <v>14</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7.045000076293945</v>
+        <v>6.96999979019165</v>
       </c>
       <c r="I25" t="n">
-        <v>3.406671361262116</v>
+        <v>3.443328654582367</v>
       </c>
       <c r="J25" t="n">
         <v>14</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19.89999961853027</v>
+        <v>19.85000038146973</v>
       </c>
       <c r="I26" t="n">
-        <v>1.889447272400348</v>
+        <v>1.89420651271625</v>
       </c>
       <c r="J26" t="n">
         <v>14</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3.319999933242798</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="I29" t="n">
-        <v>4.518072380004178</v>
+        <v>4.411764582135689</v>
       </c>
       <c r="J29" t="n">
         <v>7</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.220000028610229</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I30" t="n">
-        <v>3.828828779484834</v>
+        <v>3.794642840987262</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>37.54999923706055</v>
+        <v>37.29999923706055</v>
       </c>
       <c r="I32" t="n">
-        <v>0.399467384947255</v>
+        <v>0.4021447803434884</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5.25</v>
+        <v>5.300000190734863</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7547169539715406</v>
       </c>
       <c r="J34" t="n">
         <v>-7</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>21.95999908447266</v>
+        <v>21.70000076293945</v>
       </c>
       <c r="I35" t="n">
-        <v>1.138433562944766</v>
+        <v>1.152073692213711</v>
       </c>
       <c r="J35" t="n">
         <v>-14</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>30.29999923706055</v>
+        <v>30.5</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6435643726402855</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="J36" t="n">
         <v>-14</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.955000042915344</v>
+        <v>1.940000057220459</v>
       </c>
       <c r="I37" t="n">
-        <v>1.687979502588122</v>
+        <v>1.701030877663006</v>
       </c>
       <c r="J37" t="n">
         <v>-14</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5.230000019073486</v>
+        <v>5.25</v>
       </c>
       <c r="I38" t="n">
-        <v>5.544933058171853</v>
+        <v>5.523809523809523</v>
       </c>
       <c r="J38" t="n">
         <v>-14</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3.776000022888184</v>
+        <v>3.766000032424927</v>
       </c>
       <c r="I39" t="n">
-        <v>4.237288109908944</v>
+        <v>4.248539527945145</v>
       </c>
       <c r="J39" t="n">
         <v>-14</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2.582000017166138</v>
+        <v>2.559999942779541</v>
       </c>
       <c r="I40" t="n">
-        <v>5.367931800098119</v>
+        <v>5.41406262101373</v>
       </c>
       <c r="J40" t="n">
         <v>-14</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>54.61999893188477</v>
+        <v>54.91999816894531</v>
       </c>
       <c r="I41" t="n">
-        <v>1.153423676894716</v>
+        <v>1.147123126373729</v>
       </c>
       <c r="J41" t="n">
         <v>-14</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>6.264999866485596</v>
+        <v>6.275000095367432</v>
       </c>
       <c r="I42" t="n">
-        <v>2.23463691913108</v>
+        <v>2.231075663303274</v>
       </c>
       <c r="J42" t="n">
         <v>-14</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>16.35000038146973</v>
+        <v>16.60000038146973</v>
       </c>
       <c r="I43" t="n">
-        <v>4.770642090528714</v>
+        <v>4.698795072744092</v>
       </c>
       <c r="J43" t="n">
         <v>-14</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>61.88000106811523</v>
+        <v>63.36000061035156</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1454427899911173</v>
+        <v>0.1420454531771202</v>
       </c>
       <c r="J45" t="n">
         <v>-14</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.370000004768372</v>
+        <v>1.379999995231628</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7299270047587131</v>
+        <v>0.7246376836632911</v>
       </c>
       <c r="J46" t="n">
         <v>-14</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>6.25</v>
+        <v>6.22599983215332</v>
       </c>
       <c r="I47" t="n">
-        <v>2.9008</v>
+        <v>2.91198208942604</v>
       </c>
       <c r="J47" t="n">
         <v>-14</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.800000190734863</v>
+        <v>9.789999961853027</v>
       </c>
       <c r="I48" t="n">
-        <v>2.653061172853953</v>
+        <v>2.655771205445315</v>
       </c>
       <c r="J48" t="n">
         <v>-14</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>10.25500011444092</v>
+        <v>10.14000034332275</v>
       </c>
       <c r="I49" t="n">
-        <v>2.701121374049848</v>
+        <v>2.731755331570635</v>
       </c>
       <c r="J49" t="n">
         <v>-14</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.149999976158142</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="I50" t="n">
-        <v>1.173913067815886</v>
+        <v>1.163793136936023</v>
       </c>
       <c r="J50" t="n">
         <v>-21</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1.700000047683716</v>
+        <v>1.659999966621399</v>
       </c>
       <c r="I52" t="n">
-        <v>1.41176466628342</v>
+        <v>1.445783161601337</v>
       </c>
       <c r="J52" t="n">
         <v>-21</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.8500000238418579</v>
+        <v>0.8550000190734863</v>
       </c>
       <c r="I54" t="n">
-        <v>2.94117638809046</v>
+        <v>2.923976542958566</v>
       </c>
       <c r="J54" t="n">
         <v>-28</v>
@@ -3098,7 +3098,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3108,14 +3108,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3125,14 +3125,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3142,14 +3142,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3234,7 +3234,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3268,7 +3268,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3278,14 +3278,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3295,14 +3295,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3312,14 +3312,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3336,7 +3336,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3353,7 +3353,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3533,14 +3533,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3550,14 +3550,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3601,14 +3601,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>MEDIOLANUM GESTIONE FONDI SGR p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MEDIOLANUM GESTIONE FONDI SGR p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3880,7 +3880,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3890,14 +3890,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3948,7 +3948,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4009,14 +4009,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4026,14 +4026,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4050,7 +4050,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4060,14 +4060,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4077,14 +4077,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4101,7 +4101,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4220,7 +4220,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4237,7 +4237,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4366,14 +4366,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4383,14 +4383,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4400,14 +4400,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4434,14 +4434,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4451,14 +4451,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4475,7 +4475,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4492,7 +4492,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -4553,14 +4553,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4570,14 +4570,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4594,7 +4594,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4604,14 +4604,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4621,14 +4621,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4638,14 +4638,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4662,7 +4662,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4679,7 +4679,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4689,14 +4689,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4706,14 +4706,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4740,14 +4740,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4757,14 +4757,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4774,14 +4774,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4791,14 +4791,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4815,7 +4815,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4832,7 +4832,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4842,14 +4842,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4876,14 +4876,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4893,14 +4893,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4910,14 +4910,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4934,7 +4934,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4978,14 +4978,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5002,7 +5002,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5012,14 +5012,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5063,14 +5063,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5080,14 +5080,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5104,7 +5104,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5114,14 +5114,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5131,14 +5131,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5148,14 +5148,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5165,14 +5165,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5182,14 +5182,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5199,14 +5199,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5223,7 +5223,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5240,7 +5240,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5257,7 +5257,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5274,7 +5274,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5284,14 +5284,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5325,7 +5325,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5342,7 +5342,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5352,14 +5352,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5376,7 +5376,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5386,14 +5386,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5410,7 +5410,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5420,14 +5420,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5444,7 +5444,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5454,14 +5454,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5478,7 +5478,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CASTELLO SGR S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5495,7 +5495,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5512,7 +5512,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5522,14 +5522,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5539,14 +5539,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5563,7 +5563,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5580,7 +5580,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5590,14 +5590,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5607,14 +5607,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5631,7 +5631,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>CASTELLO SGR S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5648,7 +5648,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5675,14 +5675,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5699,7 +5699,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5716,7 +5716,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5726,14 +5726,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5750,7 +5750,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5760,14 +5760,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5818,7 +5818,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5828,14 +5828,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5845,14 +5845,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5862,14 +5862,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5879,14 +5879,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5896,14 +5896,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5913,14 +5913,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5930,14 +5930,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5954,7 +5954,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5964,14 +5964,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5988,7 +5988,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6015,14 +6015,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6039,7 +6039,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6049,14 +6049,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6073,7 +6073,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6083,14 +6083,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6100,14 +6100,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6124,7 +6124,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6158,7 +6158,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6175,7 +6175,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6192,7 +6192,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6202,14 +6202,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6219,14 +6219,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6243,7 +6243,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6270,14 +6270,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6287,14 +6287,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6311,7 +6311,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6362,7 +6362,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6379,7 +6379,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6396,7 +6396,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6413,7 +6413,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6440,14 +6440,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6457,14 +6457,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6481,7 +6481,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6491,14 +6491,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6508,14 +6508,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6532,7 +6532,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6549,7 +6549,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6566,7 +6566,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6576,14 +6576,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6593,14 +6593,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6617,7 +6617,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6642,104 +6642,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>STAR7 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005466195</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>9.699999809265137</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2.2329</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>23.01958808150907</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6750,401 +6655,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BFF Bank S.P.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Banco BPM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Bper Banca S.P.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Masi Agricola S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Neodecortech S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>OSAI Automation System S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>OSAI Automation System S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PIQUADRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RISANAMENTO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RISANAMENTO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>RISANAMENTO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Technoprobe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Tenax International S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>doValue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>